--- a/tests/TC-05/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-05/results/timetable_all_departments_even.xlsx
@@ -143,14 +143,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -182,18 +182,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -807,8 +807,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -816,62 +815,20 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -879,9 +836,59 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr"/>
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="10" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -899,8 +906,48 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="10" t="inlineStr"/>
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -908,72 +955,25 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 102
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr"/>
+      <c r="T5" s="10" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -991,14 +991,23 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>CS401
 TUT
@@ -1006,20 +1015,11 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1123,11 +1123,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1284,8 +1284,7 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -1293,62 +1292,20 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="10" t="inlineStr"/>
+      <c r="G2" s="10" t="inlineStr"/>
+      <c r="H2" s="10" t="inlineStr"/>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1356,9 +1313,59 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr"/>
+      <c r="Q2" s="10" t="inlineStr"/>
+      <c r="R2" s="10" t="inlineStr"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="10" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr"/>
+      <c r="D3" s="10" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>CS402
+LEC
+Room: 102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="10" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="10" t="inlineStr"/>
+      <c r="S3" s="10" t="inlineStr"/>
+      <c r="T3" s="10" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1376,8 +1383,48 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr"/>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="10" t="inlineStr"/>
+      <c r="R4" s="10" t="inlineStr"/>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1385,72 +1432,25 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>CS402
-LEC
-Room: 102
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="10" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="10" t="inlineStr"/>
+      <c r="S5" s="10" t="inlineStr"/>
+      <c r="T5" s="10" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1468,14 +1468,23 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>CS401
 TUT
@@ -1483,20 +1492,11 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="10" t="inlineStr"/>
+      <c r="S6" s="10" t="inlineStr"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1600,11 +1600,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1671,10 +1671,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -1815,10 +1815,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -1995,10 +1995,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>

--- a/tests/TC-05/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-05/results/timetable_all_departments_even.xlsx
@@ -78,8 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,8 +90,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,14 +143,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -182,18 +182,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -807,7 +807,138 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -815,20 +946,23 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -836,33 +970,46 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="N2" s="9" t="n"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr"/>
-      <c r="D3" s="10" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -870,156 +1017,9 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
-      <c r="O3" s="10" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr"/>
-      <c r="R3" s="10" t="inlineStr"/>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="inlineStr"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="10" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 101
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
-      <c r="T5" s="10" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1123,11 +1123,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1284,7 +1284,138 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS401
+TUT
+Room: 102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>CS401
+LEC
+Room: 101
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -1292,20 +1423,23 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="10" t="inlineStr"/>
-      <c r="F2" s="10" t="inlineStr"/>
-      <c r="G2" s="10" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
-      <c r="K2" s="10" t="inlineStr"/>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>CS401
 LEC
@@ -1313,33 +1447,46 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="N2" s="9" t="n"/>
-      <c r="O2" s="10" t="inlineStr"/>
-      <c r="P2" s="10" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr"/>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr"/>
-      <c r="D3" s="10" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t>CS402
 LEC
@@ -1347,156 +1494,9 @@
 Dr. Alpha</t>
         </is>
       </c>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
-      <c r="K3" s="10" t="inlineStr"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
-      <c r="O3" s="10" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr"/>
-      <c r="R3" s="10" t="inlineStr"/>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr"/>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="inlineStr"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="10" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>CS401
-LEC
-Room: 101
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
-      <c r="K5" s="10" t="inlineStr"/>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
-      <c r="T5" s="10" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr"/>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>CS401
-TUT
-Room: 101
-Dr. Alpha</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1600,11 +1600,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q6:S6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1671,10 +1671,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
@@ -1851,10 +1851,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS402</t>
+          <t>CS401</t>
         </is>
       </c>
     </row>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS401</t>
+          <t>CS402</t>
         </is>
       </c>
     </row>
